--- a/fundraiser_forms/016_startup_fund_donation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/016_startup_fund_donation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>created_by_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_at_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Updated By</t>
+          <t>Updated At 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_at_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Updated By</t>
+          <t>Created At 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_at_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>User Id</t>
+          <t>Updated At 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Assigned to</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>created_by_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>created_by_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>created_at_choices</t>
+          <t>created_at_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>created_at_choices</t>
+          <t>created_at_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>updated_at_choices</t>
+          <t>updated_at_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>updated_at_choices</t>
+          <t>updated_at_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
